--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -696,91 +696,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2688</v>
+        <v>3048</v>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>198.93</v>
+        <v>196.98</v>
       </c>
       <c r="F3" t="n">
-        <v>1713</v>
+        <v>1967</v>
       </c>
       <c r="G3" t="n">
-        <v>2071.82</v>
+        <v>2347.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1516</v>
+        <v>1281</v>
       </c>
       <c r="I3" t="n">
-        <v>1858</v>
+        <v>1819</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>4044</v>
+        <v>4118</v>
       </c>
       <c r="S3" t="n">
-        <v>2491</v>
+        <v>2798</v>
       </c>
       <c r="T3" t="n">
-        <v>1491</v>
+        <v>1283</v>
       </c>
       <c r="U3" t="n">
-        <v>1763</v>
+        <v>1819</v>
       </c>
       <c r="V3" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="W3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4054</v>
+        <v>4118</v>
       </c>
       <c r="AE3" t="n">
-        <v>2515</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="4">
@@ -795,91 +795,91 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>21.27</v>
+        <v>18.76</v>
       </c>
       <c r="F4" t="n">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="G4" t="n">
-        <v>1100.79</v>
+        <v>1225.91</v>
       </c>
       <c r="H4" t="n">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="I4" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="S4" t="n">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="T4" t="n">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="U4" t="n">
-        <v>514</v>
+        <v>446</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AE4" t="n">
-        <v>615</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5">
@@ -894,37 +894,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3295</v>
+        <v>3568</v>
       </c>
       <c r="D5" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="E5" t="n">
-        <v>175.13</v>
+        <v>229.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1927</v>
+        <v>2081</v>
       </c>
       <c r="G5" t="n">
-        <v>2897.54</v>
+        <v>3022.69</v>
       </c>
       <c r="H5" t="n">
-        <v>2208</v>
+        <v>1831</v>
       </c>
       <c r="I5" t="n">
-        <v>3449</v>
+        <v>3389</v>
       </c>
       <c r="J5" t="n">
-        <v>92</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -933,34 +933,34 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6152</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4225</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1756</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3456</v>
+      </c>
+      <c r="V5" t="n">
+        <v>386</v>
+      </c>
+      <c r="W5" t="n">
         <v>95</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6010</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3715</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2208</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3445</v>
-      </c>
-      <c r="V5" t="n">
-        <v>96</v>
-      </c>
-      <c r="W5" t="n">
-        <v>88</v>
-      </c>
       <c r="X5" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>422</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6010</v>
+        <v>6181</v>
       </c>
       <c r="AE5" t="n">
-        <v>3714</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="6">
@@ -993,28 +993,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2268</v>
+        <v>2559</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>84.98999999999999</v>
+        <v>103.04</v>
       </c>
       <c r="F6" t="n">
-        <v>1703</v>
+        <v>1921</v>
       </c>
       <c r="G6" t="n">
-        <v>2327.88</v>
+        <v>2529.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="I6" t="n">
-        <v>1615</v>
+        <v>1675</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1026,31 +1026,31 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="S6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="T6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="U6" t="n">
-        <v>1620</v>
+        <v>1675</v>
       </c>
       <c r="V6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1062,22 +1062,22 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="AE6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="7">
@@ -1092,91 +1092,91 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>573</v>
+        <v>718</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>28.46</v>
+        <v>28.67</v>
       </c>
       <c r="F7" t="n">
-        <v>408</v>
+        <v>555</v>
       </c>
       <c r="G7" t="n">
-        <v>1158.54</v>
+        <v>1292.62</v>
       </c>
       <c r="H7" t="n">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="I7" t="n">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1121</v>
+      </c>
+      <c r="S7" t="n">
+        <v>659</v>
+      </c>
+      <c r="T7" t="n">
+        <v>449</v>
+      </c>
+      <c r="U7" t="n">
+        <v>544</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1105</v>
-      </c>
-      <c r="S7" t="n">
-        <v>550</v>
-      </c>
-      <c r="T7" t="n">
-        <v>543</v>
-      </c>
-      <c r="U7" t="n">
-        <v>490</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
       <c r="W7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="AE7" t="n">
-        <v>549</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>682</v>
+        <v>766</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>42.34</v>
+        <v>29.72</v>
       </c>
       <c r="F8" t="n">
-        <v>322</v>
+        <v>364</v>
       </c>
       <c r="G8" t="n">
-        <v>645.11</v>
+        <v>732.77</v>
       </c>
       <c r="H8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="I8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1230,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="S8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="T8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="U8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1266,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="AE8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2193</v>
+        <v>2409</v>
       </c>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E9" t="n">
-        <v>307.67</v>
+        <v>308.85</v>
       </c>
       <c r="F9" t="n">
-        <v>1287</v>
+        <v>1429</v>
       </c>
       <c r="G9" t="n">
-        <v>1955.55</v>
+        <v>2122.51</v>
       </c>
       <c r="H9" t="n">
-        <v>2210</v>
+        <v>2105</v>
       </c>
       <c r="I9" t="n">
-        <v>2073</v>
+        <v>1928</v>
       </c>
       <c r="J9" t="n">
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1329,34 +1329,34 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4573</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2432</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1928</v>
+      </c>
+      <c r="V9" t="n">
+        <v>229</v>
+      </c>
+      <c r="W9" t="n">
+        <v>36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4540</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2305</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2210</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2074</v>
-      </c>
-      <c r="V9" t="n">
-        <v>155</v>
-      </c>
-      <c r="W9" t="n">
-        <v>27</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>2</v>
@@ -1365,16 +1365,16 @@
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>61</v>
+        <v>261</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>4539</v>
+        <v>4574</v>
       </c>
       <c r="AE9" t="n">
-        <v>2302</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="10">
@@ -1389,91 +1389,91 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3370</v>
+        <v>3700</v>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>208.5</v>
+        <v>164.23</v>
       </c>
       <c r="F10" t="n">
-        <v>2319</v>
+        <v>2577</v>
       </c>
       <c r="G10" t="n">
-        <v>2780.84</v>
+        <v>3159.61</v>
       </c>
       <c r="H10" t="n">
-        <v>3079</v>
+        <v>2889</v>
       </c>
       <c r="I10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="J10" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="S10" t="n">
-        <v>2772</v>
+        <v>3042</v>
       </c>
       <c r="T10" t="n">
-        <v>3079</v>
+        <v>2890</v>
       </c>
       <c r="U10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="V10" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="W10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="X10" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="AE10" t="n">
-        <v>2772</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="11">
@@ -1488,34 +1488,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1561</v>
+        <v>1743</v>
       </c>
       <c r="D11" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E11" t="n">
-        <v>551.97</v>
+        <v>600.2</v>
       </c>
       <c r="F11" t="n">
-        <v>824</v>
+        <v>935</v>
       </c>
       <c r="G11" t="n">
-        <v>2897.62</v>
+        <v>3103.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3915</v>
+        <v>3660</v>
       </c>
       <c r="I11" t="n">
-        <v>3813</v>
+        <v>3861</v>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1527,31 +1527,31 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="S11" t="n">
-        <v>3900</v>
+        <v>4199</v>
       </c>
       <c r="T11" t="n">
-        <v>3918</v>
+        <v>3661</v>
       </c>
       <c r="U11" t="n">
-        <v>3813</v>
+        <v>3854</v>
       </c>
       <c r="V11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="W11" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1563,16 +1563,16 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="AE11" t="n">
-        <v>3900</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="12">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1676</v>
+        <v>1883</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E12" t="n">
-        <v>213.71</v>
+        <v>224.85</v>
       </c>
       <c r="F12" t="n">
-        <v>1181</v>
+        <v>1370</v>
       </c>
       <c r="G12" t="n">
-        <v>2681.38</v>
+        <v>3003.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2373</v>
+        <v>2154</v>
       </c>
       <c r="I12" t="n">
-        <v>2316</v>
+        <v>2397</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="K12" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1626,34 +1626,34 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="S12" t="n">
-        <v>2591</v>
+        <v>2880</v>
       </c>
       <c r="T12" t="n">
-        <v>2373</v>
+        <v>2159</v>
       </c>
       <c r="U12" t="n">
-        <v>2314</v>
+        <v>2397</v>
       </c>
       <c r="V12" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="W12" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="X12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>3</v>
@@ -1662,16 +1662,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="AE12" t="n">
-        <v>2591</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="13">
@@ -1686,91 +1686,91 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1134</v>
+        <v>1363</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>40.49</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>825</v>
+        <v>1010</v>
       </c>
       <c r="G13" t="n">
-        <v>1478.65</v>
+        <v>1720.23</v>
       </c>
       <c r="H13" t="n">
-        <v>1273</v>
+        <v>1148</v>
       </c>
       <c r="I13" t="n">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="J13" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="S13" t="n">
-        <v>1080</v>
+        <v>1216</v>
       </c>
       <c r="T13" t="n">
-        <v>1274</v>
+        <v>1150</v>
       </c>
       <c r="U13" t="n">
-        <v>901</v>
+        <v>800</v>
       </c>
       <c r="V13" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="W13" t="n">
         <v>30</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="AE13" t="n">
-        <v>1079</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="14">
@@ -1785,91 +1785,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5041</v>
+        <v>5453</v>
       </c>
       <c r="D14" t="n">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="E14" t="n">
-        <v>336.88</v>
+        <v>345.84</v>
       </c>
       <c r="F14" t="n">
-        <v>3582</v>
+        <v>3916</v>
       </c>
       <c r="G14" t="n">
-        <v>4319.47</v>
+        <v>4691.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3667</v>
+        <v>3161</v>
       </c>
       <c r="I14" t="n">
-        <v>5078</v>
+        <v>5121</v>
       </c>
       <c r="J14" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="L14" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>9254</v>
+        <v>9452</v>
       </c>
       <c r="S14" t="n">
-        <v>5465</v>
+        <v>6129</v>
       </c>
       <c r="T14" t="n">
-        <v>3402</v>
+        <v>2895</v>
       </c>
       <c r="U14" t="n">
-        <v>5075</v>
+        <v>5121</v>
       </c>
       <c r="V14" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="W14" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>8899</v>
+        <v>9097</v>
       </c>
       <c r="AE14" t="n">
-        <v>5376</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="15">
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>787</v>
+        <v>853</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>3.64</v>
+        <v>4.37</v>
       </c>
       <c r="F15" t="n">
-        <v>656</v>
+        <v>710</v>
       </c>
       <c r="G15" t="n">
-        <v>1091.82</v>
+        <v>1236.05</v>
       </c>
       <c r="H15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="I15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1923,31 +1923,31 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="S15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="T15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="V15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1959,16 +1959,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="AE15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>26.95</v>
+        <v>26.63</v>
       </c>
       <c r="F16" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G16" t="n">
-        <v>384.56</v>
+        <v>383.55</v>
       </c>
       <c r="H16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -2028,22 +2028,22 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="S16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="T16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="U16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
         <v>2</v>
@@ -2064,10 +2064,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="AE16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17">
@@ -2082,91 +2082,91 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1210</v>
+        <v>1390</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>172.52</v>
+        <v>175.07</v>
       </c>
       <c r="F17" t="n">
-        <v>901</v>
+        <v>1034</v>
       </c>
       <c r="G17" t="n">
-        <v>1125.99</v>
+        <v>1207.87</v>
       </c>
       <c r="H17" t="n">
-        <v>1347</v>
+        <v>1236</v>
       </c>
       <c r="I17" t="n">
-        <v>1255</v>
+        <v>1149</v>
       </c>
       <c r="J17" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2753</v>
+        <v>2781</v>
       </c>
       <c r="S17" t="n">
-        <v>1400</v>
+        <v>1541</v>
       </c>
       <c r="T17" t="n">
-        <v>1348</v>
+        <v>1230</v>
       </c>
       <c r="U17" t="n">
-        <v>1255</v>
+        <v>1127</v>
       </c>
       <c r="V17" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2753</v>
+        <v>2784</v>
       </c>
       <c r="AE17" t="n">
-        <v>1399</v>
+        <v>1550</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,157 +417,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Berhasil Didata (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Usaha Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga Didata</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Usaha dalam Keluarga Didata</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -711,19 +699,19 @@
         <v>2347.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1281</v>
+        <v>1169</v>
       </c>
       <c r="I3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="J3" t="n">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -741,25 +729,25 @@
         <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="S3" t="n">
-        <v>2798</v>
+        <v>2924</v>
       </c>
       <c r="T3" t="n">
-        <v>1283</v>
+        <v>1169</v>
       </c>
       <c r="U3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="V3" t="n">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -777,10 +765,10 @@
         <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="AE3" t="n">
-        <v>2795</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="4">
@@ -810,52 +798,52 @@
         <v>1225.91</v>
       </c>
       <c r="H4" t="n">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="I4" t="n">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="S4" t="n">
-        <v>661</v>
+        <v>744</v>
       </c>
       <c r="T4" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="U4" t="n">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="W4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -864,22 +852,22 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="AE4" t="n">
-        <v>670</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5">
@@ -909,22 +897,22 @@
         <v>3022.69</v>
       </c>
       <c r="H5" t="n">
-        <v>1831</v>
+        <v>1605</v>
       </c>
       <c r="I5" t="n">
-        <v>3389</v>
+        <v>3789</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -933,34 +921,34 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>6152</v>
+        <v>6241</v>
       </c>
       <c r="S5" t="n">
-        <v>4225</v>
+        <v>4550</v>
       </c>
       <c r="T5" t="n">
-        <v>1756</v>
+        <v>1605</v>
       </c>
       <c r="U5" t="n">
-        <v>3456</v>
+        <v>3789</v>
       </c>
       <c r="V5" t="n">
-        <v>386</v>
+        <v>104</v>
       </c>
       <c r="W5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="X5" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -969,16 +957,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6181</v>
+        <v>6240</v>
       </c>
       <c r="AE5" t="n">
-        <v>4330</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="6">
@@ -1008,19 +996,19 @@
         <v>2529.5</v>
       </c>
       <c r="H6" t="n">
-        <v>902</v>
+        <v>805</v>
       </c>
       <c r="I6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="J6" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1038,25 +1026,25 @@
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="S6" t="n">
-        <v>2219</v>
+        <v>2353</v>
       </c>
       <c r="T6" t="n">
-        <v>902</v>
+        <v>806</v>
       </c>
       <c r="U6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="V6" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1074,10 +1062,10 @@
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="AE6" t="n">
-        <v>2219</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="7">
@@ -1107,19 +1095,19 @@
         <v>1292.62</v>
       </c>
       <c r="H7" t="n">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="I7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1137,25 +1125,25 @@
         <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="S7" t="n">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="T7" t="n">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="U7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="W7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1173,10 +1161,10 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="AE7" t="n">
-        <v>658</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -1206,25 +1194,25 @@
         <v>732.77</v>
       </c>
       <c r="H8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="I8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1236,31 +1224,31 @@
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="S8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="T8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="U8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1272,10 +1260,10 @@
         <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AE8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
     </row>
     <row r="9">
@@ -1305,22 +1293,22 @@
         <v>2122.51</v>
       </c>
       <c r="H9" t="n">
-        <v>2105</v>
+        <v>2049</v>
       </c>
       <c r="I9" t="n">
-        <v>1928</v>
+        <v>1986</v>
       </c>
       <c r="J9" t="n">
         <v>223</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1329,34 +1317,34 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="Q9" t="n">
         <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>4573</v>
+        <v>4596</v>
       </c>
       <c r="S9" t="n">
-        <v>2432</v>
+        <v>2510</v>
       </c>
       <c r="T9" t="n">
-        <v>2100</v>
+        <v>2049</v>
       </c>
       <c r="U9" t="n">
-        <v>1928</v>
+        <v>1990</v>
       </c>
       <c r="V9" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="W9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>2</v>
@@ -1365,16 +1353,16 @@
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AC9" t="n">
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>4574</v>
+        <v>4596</v>
       </c>
       <c r="AE9" t="n">
-        <v>2438</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="10">
@@ -1404,76 +1392,76 @@
         <v>3159.61</v>
       </c>
       <c r="H10" t="n">
-        <v>2889</v>
+        <v>2813</v>
       </c>
       <c r="I10" t="n">
-        <v>2279</v>
+        <v>2427</v>
       </c>
       <c r="J10" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="S10" t="n">
-        <v>3042</v>
+        <v>3149</v>
       </c>
       <c r="T10" t="n">
-        <v>2890</v>
+        <v>2808</v>
       </c>
       <c r="U10" t="n">
-        <v>2279</v>
+        <v>2424</v>
       </c>
       <c r="V10" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="W10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="AE10" t="n">
-        <v>3040</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="11">
@@ -1503,19 +1491,19 @@
         <v>3103.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3660</v>
+        <v>3560</v>
       </c>
       <c r="I11" t="n">
-        <v>3861</v>
+        <v>3868</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1527,31 +1515,31 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="S11" t="n">
-        <v>4199</v>
+        <v>4368</v>
       </c>
       <c r="T11" t="n">
-        <v>3661</v>
+        <v>3560</v>
       </c>
       <c r="U11" t="n">
-        <v>3854</v>
+        <v>3868</v>
       </c>
       <c r="V11" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="W11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1563,16 +1551,16 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>227</v>
+        <v>456</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="AE11" t="n">
-        <v>4198</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="12">
@@ -1602,25 +1590,25 @@
         <v>3003.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2154</v>
+        <v>2077</v>
       </c>
       <c r="I12" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="J12" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K12" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1632,31 +1620,31 @@
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="S12" t="n">
-        <v>2880</v>
+        <v>2983</v>
       </c>
       <c r="T12" t="n">
-        <v>2159</v>
+        <v>2077</v>
       </c>
       <c r="U12" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="V12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="W12" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="X12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1668,10 +1656,10 @@
         <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="AE12" t="n">
-        <v>2874</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="13">
@@ -1701,22 +1689,22 @@
         <v>1720.23</v>
       </c>
       <c r="H13" t="n">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="I13" t="n">
-        <v>800</v>
+        <v>844</v>
       </c>
       <c r="J13" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
@@ -1725,34 +1713,34 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13" t="n">
         <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="S13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="T13" t="n">
-        <v>1150</v>
+        <v>1115</v>
       </c>
       <c r="U13" t="n">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="V13" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="W13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="X13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>3</v>
@@ -1761,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AC13" t="n">
         <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="AE13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="14">
@@ -1800,22 +1788,22 @@
         <v>4691.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3161</v>
+        <v>2948</v>
       </c>
       <c r="I14" t="n">
-        <v>5121</v>
+        <v>5564</v>
       </c>
       <c r="J14" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -1824,34 +1812,34 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>9452</v>
+        <v>9558</v>
       </c>
       <c r="S14" t="n">
-        <v>6129</v>
+        <v>6511</v>
       </c>
       <c r="T14" t="n">
-        <v>2895</v>
+        <v>2682</v>
       </c>
       <c r="U14" t="n">
-        <v>5121</v>
+        <v>5561</v>
       </c>
       <c r="V14" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="W14" t="n">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>11</v>
@@ -1860,16 +1848,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>9097</v>
+        <v>9203</v>
       </c>
       <c r="AE14" t="n">
-        <v>6041</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="15">
@@ -1899,13 +1887,13 @@
         <v>1236.05</v>
       </c>
       <c r="H15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="I15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1929,19 +1917,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="S15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="T15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="U15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1965,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
     </row>
     <row r="16">
@@ -1998,19 +1986,19 @@
         <v>383.55</v>
       </c>
       <c r="H16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2025,28 +2013,28 @@
         <v>20</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>622</v>
       </c>
       <c r="S16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="T16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="U16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="V16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2061,13 +2049,13 @@
         <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>622</v>
       </c>
       <c r="AE16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17">
@@ -2097,76 +2085,76 @@
         <v>1207.87</v>
       </c>
       <c r="H17" t="n">
-        <v>1236</v>
+        <v>1162</v>
       </c>
       <c r="I17" t="n">
-        <v>1149</v>
+        <v>1195</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2781</v>
+        <v>2805</v>
       </c>
       <c r="S17" t="n">
-        <v>1541</v>
+        <v>1640</v>
       </c>
       <c r="T17" t="n">
-        <v>1230</v>
+        <v>1163</v>
       </c>
       <c r="U17" t="n">
-        <v>1127</v>
+        <v>1195</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AC17" t="n">
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2784</v>
+        <v>2804</v>
       </c>
       <c r="AE17" t="n">
-        <v>1550</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -429,27 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Jumlah Usaha Berhasil Didata (semua status keberadaan usaha)</t>
+          <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Jumlah Usaha Didata</t>
+          <t>Jumlah Usaha BKU</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Persentase Usaha Didata</t>
+          <t>Persentase Usaha BKU</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Jumlah Usaha dalam Keluarga Didata</t>
+          <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Persentase Usaha dalam Keluarga Didata</t>
+          <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -684,91 +684,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3048</v>
+        <v>4059</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>196.98</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>1967</v>
+        <v>2713</v>
       </c>
       <c r="G3" t="n">
-        <v>2347.18</v>
+        <v>3080.78</v>
       </c>
       <c r="H3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="I3" t="n">
-        <v>2221</v>
+        <v>2752</v>
       </c>
       <c r="J3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="S3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
       <c r="T3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="U3" t="n">
-        <v>2221</v>
+        <v>2754</v>
       </c>
       <c r="V3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="W3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="AE3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="4">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>483</v>
+        <v>954</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>18.76</v>
+        <v>48.83</v>
       </c>
       <c r="F4" t="n">
-        <v>378</v>
+        <v>798</v>
       </c>
       <c r="G4" t="n">
-        <v>1225.91</v>
+        <v>1621.72</v>
       </c>
       <c r="H4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="I4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="J4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -822,31 +822,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="S4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
       <c r="T4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="U4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -858,16 +858,16 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="AC4" t="n">
         <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="AE4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5">
@@ -882,34 +882,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3568</v>
+        <v>5109</v>
       </c>
       <c r="D5" t="n">
-        <v>141</v>
+        <v>346</v>
       </c>
       <c r="E5" t="n">
-        <v>229.3</v>
+        <v>368.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2081</v>
+        <v>2941</v>
       </c>
       <c r="G5" t="n">
-        <v>3022.69</v>
+        <v>3886.36</v>
       </c>
       <c r="H5" t="n">
-        <v>1605</v>
+        <v>957</v>
       </c>
       <c r="I5" t="n">
-        <v>3789</v>
+        <v>4368</v>
       </c>
       <c r="J5" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -921,31 +921,31 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>6241</v>
+        <v>6487</v>
       </c>
       <c r="S5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
       <c r="T5" t="n">
-        <v>1605</v>
+        <v>959</v>
       </c>
       <c r="U5" t="n">
-        <v>3789</v>
+        <v>4368</v>
       </c>
       <c r="V5" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="W5" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="X5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -957,16 +957,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6240</v>
+        <v>6487</v>
       </c>
       <c r="AE5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -981,91 +981,91 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2559</v>
+        <v>3529</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="E6" t="n">
-        <v>103.04</v>
+        <v>178.26</v>
       </c>
       <c r="F6" t="n">
-        <v>1921</v>
+        <v>2619</v>
       </c>
       <c r="G6" t="n">
-        <v>2529.5</v>
+        <v>2988.02</v>
       </c>
       <c r="H6" t="n">
-        <v>805</v>
+        <v>382</v>
       </c>
       <c r="I6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="J6" t="n">
+        <v>121</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22</v>
+      </c>
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="S6" t="n">
-        <v>2353</v>
+        <v>2924</v>
       </c>
       <c r="T6" t="n">
-        <v>806</v>
+        <v>383</v>
       </c>
       <c r="U6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="AE6" t="n">
-        <v>2352</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="7">
@@ -1080,34 +1080,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>718</v>
+        <v>1025</v>
       </c>
       <c r="D7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91.26000000000002</v>
+      </c>
+      <c r="F7" t="n">
+        <v>831</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1552.14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>310</v>
+      </c>
+      <c r="I7" t="n">
+        <v>694</v>
+      </c>
+      <c r="J7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="F7" t="n">
-        <v>555</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1292.62</v>
-      </c>
-      <c r="H7" t="n">
-        <v>421</v>
-      </c>
-      <c r="I7" t="n">
-        <v>558</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31</v>
-      </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1119,31 +1119,31 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1158</v>
+      </c>
+      <c r="S7" t="n">
+        <v>832</v>
+      </c>
+      <c r="T7" t="n">
+        <v>310</v>
+      </c>
+      <c r="U7" t="n">
+        <v>694</v>
+      </c>
+      <c r="V7" t="n">
         <v>8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="S7" t="n">
-        <v>693</v>
-      </c>
-      <c r="T7" t="n">
-        <v>422</v>
-      </c>
-      <c r="U7" t="n">
-        <v>558</v>
-      </c>
-      <c r="V7" t="n">
-        <v>31</v>
-      </c>
       <c r="W7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="AE7" t="n">
-        <v>692</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -1179,91 +1179,91 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>766</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>29.72</v>
+        <v>46.71</v>
       </c>
       <c r="F8" t="n">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="G8" t="n">
-        <v>732.77</v>
+        <v>1024.19</v>
       </c>
       <c r="H8" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="I8" t="n">
-        <v>504</v>
+        <v>644</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S8" t="n">
+        <v>784</v>
+      </c>
+      <c r="T8" t="n">
+        <v>280</v>
+      </c>
+      <c r="U8" t="n">
+        <v>644</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>112</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1019</v>
-      </c>
-      <c r="S8" t="n">
-        <v>634</v>
-      </c>
-      <c r="T8" t="n">
-        <v>384</v>
-      </c>
-      <c r="U8" t="n">
-        <v>504</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1019</v>
+        <v>1065</v>
       </c>
       <c r="AE8" t="n">
-        <v>634</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9">
@@ -1278,91 +1278,91 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2409</v>
+        <v>3394</v>
       </c>
       <c r="D9" t="n">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="E9" t="n">
-        <v>308.85</v>
+        <v>300.61</v>
       </c>
       <c r="F9" t="n">
-        <v>1429</v>
+        <v>2103</v>
       </c>
       <c r="G9" t="n">
-        <v>2122.51</v>
+        <v>3152.57</v>
       </c>
       <c r="H9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="I9" t="n">
-        <v>1986</v>
+        <v>2443</v>
       </c>
       <c r="J9" t="n">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="S9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
       <c r="T9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="U9" t="n">
-        <v>1990</v>
+        <v>2443</v>
       </c>
       <c r="V9" t="n">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="W9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="AE9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="10">
@@ -1377,91 +1377,91 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3700</v>
+        <v>5829</v>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="E10" t="n">
-        <v>164.23</v>
+        <v>261.38</v>
       </c>
       <c r="F10" t="n">
-        <v>2577</v>
+        <v>4224</v>
       </c>
       <c r="G10" t="n">
-        <v>3159.61</v>
+        <v>4243.03</v>
       </c>
       <c r="H10" t="n">
-        <v>2813</v>
+        <v>1980</v>
       </c>
       <c r="I10" t="n">
-        <v>2427</v>
+        <v>3260</v>
       </c>
       <c r="J10" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5997</v>
+        <v>6348</v>
       </c>
       <c r="S10" t="n">
-        <v>3149</v>
+        <v>4331</v>
       </c>
       <c r="T10" t="n">
-        <v>2808</v>
+        <v>1980</v>
       </c>
       <c r="U10" t="n">
-        <v>2424</v>
+        <v>3260</v>
       </c>
       <c r="V10" t="n">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="W10" t="n">
         <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5997</v>
+        <v>6347</v>
       </c>
       <c r="AE10" t="n">
-        <v>3152</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="11">
@@ -1476,91 +1476,91 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1743</v>
+        <v>2800</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>525</v>
       </c>
       <c r="E11" t="n">
-        <v>600.2</v>
+        <v>1104.51</v>
       </c>
       <c r="F11" t="n">
-        <v>935</v>
+        <v>1397</v>
       </c>
       <c r="G11" t="n">
-        <v>3103.02</v>
+        <v>4044.11</v>
       </c>
       <c r="H11" t="n">
-        <v>3560</v>
+        <v>2620</v>
       </c>
       <c r="I11" t="n">
-        <v>3868</v>
+        <v>5034</v>
       </c>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q11" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>456</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>8450</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5652</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2620</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5034</v>
+      </c>
+      <c r="V11" t="n">
+        <v>48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>176</v>
+      </c>
+      <c r="X11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="n">
-        <v>8064</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4368</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3560</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3868</v>
-      </c>
-      <c r="V11" t="n">
-        <v>28</v>
-      </c>
-      <c r="W11" t="n">
-        <v>136</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>542</v>
+      </c>
+      <c r="AC11" t="n">
         <v>6</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>456</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5</v>
-      </c>
       <c r="AD11" t="n">
-        <v>8064</v>
+        <v>8448</v>
       </c>
       <c r="AE11" t="n">
-        <v>4368</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="12">
@@ -1575,91 +1575,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1883</v>
+        <v>2810</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="E12" t="n">
-        <v>224.85</v>
+        <v>440.02</v>
       </c>
       <c r="F12" t="n">
-        <v>1370</v>
+        <v>2073</v>
       </c>
       <c r="G12" t="n">
-        <v>3003.4</v>
+        <v>4132.93</v>
       </c>
       <c r="H12" t="n">
-        <v>2077</v>
+        <v>1416</v>
       </c>
       <c r="I12" t="n">
-        <v>2487</v>
+        <v>3241</v>
       </c>
       <c r="J12" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>453</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="S12" t="n">
-        <v>2983</v>
+        <v>3797</v>
       </c>
       <c r="T12" t="n">
-        <v>2077</v>
+        <v>1418</v>
       </c>
       <c r="U12" t="n">
-        <v>2487</v>
+        <v>3241</v>
       </c>
       <c r="V12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="W12" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="X12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>453</v>
+      </c>
+      <c r="AC12" t="n">
         <v>5</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>371</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
       <c r="AD12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="AE12" t="n">
-        <v>2983</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="13">
@@ -1674,91 +1674,91 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1363</v>
+        <v>2092</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1010</v>
+        <v>1615</v>
       </c>
       <c r="G13" t="n">
-        <v>1720.23</v>
+        <v>2410.08</v>
       </c>
       <c r="H13" t="n">
-        <v>1115</v>
+        <v>751</v>
       </c>
       <c r="I13" t="n">
-        <v>844</v>
+        <v>1250</v>
       </c>
       <c r="J13" t="n">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R13" t="n">
-        <v>2406</v>
+        <v>2445</v>
       </c>
       <c r="S13" t="n">
-        <v>1266</v>
+        <v>1608</v>
       </c>
       <c r="T13" t="n">
-        <v>1115</v>
+        <v>751</v>
       </c>
       <c r="U13" t="n">
-        <v>841</v>
+        <v>1248</v>
       </c>
       <c r="V13" t="n">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AC13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>2406</v>
+        <v>2445</v>
       </c>
       <c r="AE13" t="n">
-        <v>1266</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="14">
@@ -1773,91 +1773,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5453</v>
+        <v>8544</v>
       </c>
       <c r="D14" t="n">
-        <v>271</v>
+        <v>484</v>
       </c>
       <c r="E14" t="n">
-        <v>345.84</v>
+        <v>531.38</v>
       </c>
       <c r="F14" t="n">
-        <v>3916</v>
+        <v>6358</v>
       </c>
       <c r="G14" t="n">
-        <v>4691.58</v>
+        <v>6410.83</v>
       </c>
       <c r="H14" t="n">
-        <v>2948</v>
+        <v>1393</v>
       </c>
       <c r="I14" t="n">
-        <v>5564</v>
+        <v>7134</v>
       </c>
       <c r="J14" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>9558</v>
+        <v>9735</v>
       </c>
       <c r="S14" t="n">
-        <v>6511</v>
+        <v>8195</v>
       </c>
       <c r="T14" t="n">
-        <v>2682</v>
+        <v>1394</v>
       </c>
       <c r="U14" t="n">
-        <v>5561</v>
+        <v>7134</v>
       </c>
       <c r="V14" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="W14" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="AC14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>9203</v>
+        <v>9735</v>
       </c>
       <c r="AE14" t="n">
-        <v>6424</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="15">
@@ -1872,28 +1872,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>853</v>
+        <v>1241</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>4.37</v>
+        <v>15.3</v>
       </c>
       <c r="F15" t="n">
-        <v>710</v>
+        <v>1049</v>
       </c>
       <c r="G15" t="n">
-        <v>1236.05</v>
+        <v>1611.33</v>
       </c>
       <c r="H15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="I15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1911,25 +1911,25 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="S15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
       <c r="T15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="U15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1947,16 +1947,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="AE15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">
@@ -1971,31 +1971,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>26.63</v>
+        <v>30.63</v>
       </c>
       <c r="F16" t="n">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="G16" t="n">
-        <v>383.55</v>
+        <v>475.55</v>
       </c>
       <c r="H16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -2010,28 +2010,28 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="S16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="T16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="U16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
         <v>3</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AE16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17">
@@ -2070,37 +2070,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1390</v>
+        <v>2184</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="E17" t="n">
-        <v>175.07</v>
+        <v>252.69</v>
       </c>
       <c r="F17" t="n">
-        <v>1034</v>
+        <v>1651</v>
       </c>
       <c r="G17" t="n">
-        <v>1207.87</v>
+        <v>1833.13</v>
       </c>
       <c r="H17" t="n">
-        <v>1162</v>
+        <v>815</v>
       </c>
       <c r="I17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
         <v>8</v>
@@ -2109,34 +2109,34 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2805</v>
+        <v>2921</v>
       </c>
       <c r="S17" t="n">
-        <v>1640</v>
+        <v>2106</v>
       </c>
       <c r="T17" t="n">
-        <v>1163</v>
+        <v>815</v>
       </c>
       <c r="U17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="V17" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
         <v>8</v>
@@ -2145,16 +2145,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="AC17" t="n">
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2804</v>
+        <v>2921</v>
       </c>
       <c r="AE17" t="n">
-        <v>1638</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,157 +429,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,157 +417,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,157 +429,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha (semua status keberadaan usaha)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha Dalam Keluarga</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Persentase Usaha Dalam Keluarga</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha dalam Keluarga</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Persentase Usaha dalam Keluarga</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -585,13 +597,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>55.56</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -684,91 +696,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4059</v>
+        <v>5052</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>387</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>243.32</v>
       </c>
       <c r="F3" t="n">
-        <v>2713</v>
+        <v>3355</v>
       </c>
       <c r="G3" t="n">
-        <v>3080.78</v>
+        <v>3239.51</v>
       </c>
       <c r="H3" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>2752</v>
+        <v>3545</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="K3" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
-        <v>4258</v>
+        <v>4454</v>
       </c>
       <c r="S3" t="n">
-        <v>3560</v>
+        <v>4424</v>
       </c>
       <c r="T3" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="U3" t="n">
-        <v>2754</v>
+        <v>3533</v>
       </c>
       <c r="V3" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="W3" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="AC3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AD3" t="n">
-        <v>4258</v>
+        <v>4453</v>
       </c>
       <c r="AE3" t="n">
-        <v>3560</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="4">
@@ -783,34 +795,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>954</v>
+        <v>1101</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>48.83</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>798</v>
+        <v>912</v>
       </c>
       <c r="G4" t="n">
-        <v>1621.72</v>
+        <v>1909.68</v>
       </c>
       <c r="H4" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="I4" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -822,31 +834,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="S4" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
       <c r="T4" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="U4" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="W4" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -858,16 +870,16 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="AE4" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="5">
@@ -882,91 +894,91 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5109</v>
+        <v>6160</v>
       </c>
       <c r="D5" t="n">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="E5" t="n">
-        <v>368.01</v>
+        <v>410.07</v>
       </c>
       <c r="F5" t="n">
-        <v>2941</v>
+        <v>3504</v>
       </c>
       <c r="G5" t="n">
-        <v>3886.36</v>
+        <v>4298.95</v>
       </c>
       <c r="H5" t="n">
-        <v>957</v>
+        <v>112</v>
       </c>
       <c r="I5" t="n">
-        <v>4368</v>
+        <v>5543</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="S5" t="n">
-        <v>5430</v>
+        <v>6662</v>
       </c>
       <c r="T5" t="n">
-        <v>959</v>
+        <v>113</v>
       </c>
       <c r="U5" t="n">
-        <v>4368</v>
+        <v>5543</v>
       </c>
       <c r="V5" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="W5" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="X5" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="AE5" t="n">
-        <v>5430</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="6">
@@ -981,91 +993,91 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3529</v>
+        <v>4212</v>
       </c>
       <c r="D6" t="n">
-        <v>232</v>
+        <v>382</v>
       </c>
       <c r="E6" t="n">
-        <v>178.26</v>
+        <v>215.96</v>
       </c>
       <c r="F6" t="n">
-        <v>2619</v>
+        <v>3027</v>
       </c>
       <c r="G6" t="n">
-        <v>2988.02</v>
+        <v>3137.63</v>
       </c>
       <c r="H6" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="J6" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="S6" t="n">
-        <v>2924</v>
+        <v>3521</v>
       </c>
       <c r="T6" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="V6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="AE6" t="n">
-        <v>2923</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="7">
@@ -1080,91 +1092,91 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1025</v>
+        <v>1372</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
-        <v>91.26000000000002</v>
+        <v>124.07</v>
       </c>
       <c r="F7" t="n">
-        <v>831</v>
+        <v>1130</v>
       </c>
       <c r="G7" t="n">
-        <v>1552.14</v>
+        <v>1964.76</v>
       </c>
       <c r="H7" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="I7" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
         <v>16</v>
       </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="S7" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
       <c r="T7" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="U7" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
+        <v>7</v>
+      </c>
+      <c r="X7" t="n">
         <v>16</v>
       </c>
-      <c r="X7" t="n">
-        <v>9</v>
-      </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="AE7" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="8">
@@ -1179,31 +1191,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>1366</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>46.71</v>
+        <v>76.42999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>506</v>
+        <v>691</v>
       </c>
       <c r="G8" t="n">
-        <v>1024.19</v>
+        <v>1139.55</v>
       </c>
       <c r="H8" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="I8" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1218,28 +1230,28 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="S8" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
       <c r="T8" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="U8" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1254,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="AE8" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="9">
@@ -1278,91 +1290,91 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3394</v>
+        <v>4759</v>
       </c>
       <c r="D9" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>300.61</v>
+        <v>226.55</v>
       </c>
       <c r="F9" t="n">
-        <v>2103</v>
+        <v>3082</v>
       </c>
       <c r="G9" t="n">
-        <v>3152.57</v>
+        <v>3722.82</v>
       </c>
       <c r="H9" t="n">
-        <v>1630</v>
+        <v>745</v>
       </c>
       <c r="I9" t="n">
-        <v>2443</v>
+        <v>3557</v>
       </c>
       <c r="J9" t="n">
-        <v>289</v>
+        <v>205</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="S9" t="n">
-        <v>3153</v>
+        <v>4402</v>
       </c>
       <c r="T9" t="n">
-        <v>1630</v>
+        <v>748</v>
       </c>
       <c r="U9" t="n">
-        <v>2443</v>
+        <v>3555</v>
       </c>
       <c r="V9" t="n">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="W9" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="AE9" t="n">
-        <v>3153</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="10">
@@ -1377,91 +1389,91 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5829</v>
+        <v>7784</v>
       </c>
       <c r="D10" t="n">
-        <v>197</v>
+        <v>440</v>
       </c>
       <c r="E10" t="n">
-        <v>261.38</v>
+        <v>345.73</v>
       </c>
       <c r="F10" t="n">
-        <v>4224</v>
+        <v>5439</v>
       </c>
       <c r="G10" t="n">
-        <v>4243.03</v>
+        <v>4819.38</v>
       </c>
       <c r="H10" t="n">
-        <v>1980</v>
+        <v>742</v>
       </c>
       <c r="I10" t="n">
-        <v>3260</v>
+        <v>4117</v>
       </c>
       <c r="J10" t="n">
-        <v>296</v>
+        <v>780</v>
       </c>
       <c r="K10" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="L10" t="n">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>6348</v>
+        <v>6749</v>
       </c>
       <c r="S10" t="n">
-        <v>4331</v>
+        <v>5894</v>
       </c>
       <c r="T10" t="n">
-        <v>1980</v>
+        <v>742</v>
       </c>
       <c r="U10" t="n">
-        <v>3260</v>
+        <v>4117</v>
       </c>
       <c r="V10" t="n">
-        <v>295</v>
+        <v>780</v>
       </c>
       <c r="W10" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="X10" t="n">
-        <v>198</v>
+        <v>335</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>6347</v>
+        <v>6749</v>
       </c>
       <c r="AE10" t="n">
-        <v>4330</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="11">
@@ -1476,91 +1488,91 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2800</v>
+        <v>4063</v>
       </c>
       <c r="D11" t="n">
-        <v>525</v>
+        <v>976</v>
       </c>
       <c r="E11" t="n">
-        <v>1104.51</v>
+        <v>1163.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1397</v>
+        <v>1778</v>
       </c>
       <c r="G11" t="n">
-        <v>4044.11</v>
+        <v>4284.68</v>
       </c>
       <c r="H11" t="n">
-        <v>2620</v>
+        <v>980</v>
       </c>
       <c r="I11" t="n">
-        <v>5034</v>
+        <v>6975</v>
       </c>
       <c r="J11" t="n">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="K11" t="n">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>8450</v>
+        <v>8991</v>
       </c>
       <c r="S11" t="n">
-        <v>5652</v>
+        <v>7916</v>
       </c>
       <c r="T11" t="n">
-        <v>2620</v>
+        <v>981</v>
       </c>
       <c r="U11" t="n">
-        <v>5034</v>
+        <v>6975</v>
       </c>
       <c r="V11" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="W11" t="n">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>8448</v>
+        <v>8991</v>
       </c>
       <c r="AE11" t="n">
-        <v>5652</v>
+        <v>7915</v>
       </c>
     </row>
     <row r="12">
@@ -1575,91 +1587,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2810</v>
+        <v>3536</v>
       </c>
       <c r="D12" t="n">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="E12" t="n">
-        <v>440.02</v>
+        <v>620.52</v>
       </c>
       <c r="F12" t="n">
-        <v>2073</v>
+        <v>2568</v>
       </c>
       <c r="G12" t="n">
-        <v>4132.93</v>
+        <v>4522.81</v>
       </c>
       <c r="H12" t="n">
-        <v>1416</v>
+        <v>432</v>
       </c>
       <c r="I12" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="J12" t="n">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="K12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="S12" t="n">
-        <v>3797</v>
+        <v>5057</v>
       </c>
       <c r="T12" t="n">
-        <v>1418</v>
+        <v>434</v>
       </c>
       <c r="U12" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="V12" t="n">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="W12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="AE12" t="n">
-        <v>3795</v>
+        <v>5055</v>
       </c>
     </row>
     <row r="13">
@@ -1674,37 +1686,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2092</v>
+        <v>3104</v>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>92.34999999999999</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1615</v>
+        <v>2429</v>
       </c>
       <c r="G13" t="n">
-        <v>2410.08</v>
+        <v>3072.17</v>
       </c>
       <c r="H13" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="I13" t="n">
-        <v>1250</v>
+        <v>1652</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="K13" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="L13" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -1713,34 +1725,34 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="S13" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
       <c r="T13" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="U13" t="n">
-        <v>1248</v>
+        <v>1652</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="W13" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="X13" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
@@ -1749,16 +1761,16 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD13" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="AE13" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="14">
@@ -1773,91 +1785,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8544</v>
+        <v>10443</v>
       </c>
       <c r="D14" t="n">
-        <v>484</v>
+        <v>738</v>
       </c>
       <c r="E14" t="n">
-        <v>531.38</v>
+        <v>682.41</v>
       </c>
       <c r="F14" t="n">
-        <v>6358</v>
+        <v>7740</v>
       </c>
       <c r="G14" t="n">
-        <v>6410.83</v>
+        <v>6969.06</v>
       </c>
       <c r="H14" t="n">
-        <v>1393</v>
+        <v>149</v>
       </c>
       <c r="I14" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="J14" t="n">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="K14" t="n">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="S14" t="n">
-        <v>8195</v>
+        <v>10172</v>
       </c>
       <c r="T14" t="n">
-        <v>1394</v>
+        <v>149</v>
       </c>
       <c r="U14" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="V14" t="n">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="W14" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="AE14" t="n">
-        <v>8195</v>
+        <v>10171</v>
       </c>
     </row>
     <row r="15">
@@ -1872,28 +1884,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1241</v>
+        <v>1385</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1049</v>
+        <v>1172</v>
       </c>
       <c r="G15" t="n">
-        <v>1611.33</v>
+        <v>1692.39</v>
       </c>
       <c r="H15" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1905,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1917,19 +1929,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="S15" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
       <c r="T15" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="V15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1941,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -1953,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="AE15" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="16">
@@ -1971,34 +1983,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>30.63</v>
+        <v>128.85</v>
       </c>
       <c r="F16" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="G16" t="n">
-        <v>475.55</v>
+        <v>479.11</v>
       </c>
       <c r="H16" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="I16" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2016,25 +2028,25 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="S16" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="T16" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="U16" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2052,10 +2064,10 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="AE16" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17">
@@ -2070,91 +2082,91 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2184</v>
+        <v>3039</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E17" t="n">
-        <v>252.69</v>
+        <v>264.9</v>
       </c>
       <c r="F17" t="n">
-        <v>1651</v>
+        <v>2375</v>
       </c>
       <c r="G17" t="n">
-        <v>1833.13</v>
+        <v>2542.17</v>
       </c>
       <c r="H17" t="n">
-        <v>815</v>
+        <v>275</v>
       </c>
       <c r="I17" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="J17" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>516</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>24</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>492</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
       <c r="R17" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="S17" t="n">
-        <v>2106</v>
+        <v>2734</v>
       </c>
       <c r="T17" t="n">
-        <v>815</v>
+        <v>276</v>
       </c>
       <c r="U17" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="V17" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>516</v>
+      </c>
+      <c r="AC17" t="n">
         <v>4</v>
       </c>
-      <c r="Y17" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>492</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3</v>
-      </c>
       <c r="AD17" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="AE17" t="n">
-        <v>2106</v>
+        <v>2733</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROPORSI USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,157 +417,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha (semua status keberadaan usaha)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha dalam Keluarga</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Persentase Usaha dalam Keluarga</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha Dalam Keluarga</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Persentase Usaha Dalam Keluarga</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -597,13 +585,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>55.56</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -696,91 +684,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5052</v>
+        <v>4059</v>
       </c>
       <c r="D3" t="n">
-        <v>387</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>243.32</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>3355</v>
+        <v>2713</v>
       </c>
       <c r="G3" t="n">
-        <v>3239.51</v>
+        <v>3080.78</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="I3" t="n">
-        <v>3545</v>
+        <v>2752</v>
       </c>
       <c r="J3" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>4454</v>
+        <v>4258</v>
       </c>
       <c r="S3" t="n">
-        <v>4424</v>
+        <v>3560</v>
       </c>
       <c r="T3" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="U3" t="n">
-        <v>3533</v>
+        <v>2754</v>
       </c>
       <c r="V3" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="AC3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>4453</v>
+        <v>4258</v>
       </c>
       <c r="AE3" t="n">
-        <v>4423</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="4">
@@ -795,34 +783,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1101</v>
+        <v>954</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>71.26000000000001</v>
+        <v>48.83</v>
       </c>
       <c r="F4" t="n">
-        <v>912</v>
+        <v>798</v>
       </c>
       <c r="G4" t="n">
-        <v>1909.68</v>
+        <v>1621.72</v>
       </c>
       <c r="H4" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="I4" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -834,31 +822,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="S4" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
       <c r="T4" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="U4" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -870,16 +858,16 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="AE4" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5">
@@ -894,91 +882,91 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6160</v>
+        <v>5109</v>
       </c>
       <c r="D5" t="n">
-        <v>431</v>
+        <v>346</v>
       </c>
       <c r="E5" t="n">
-        <v>410.07</v>
+        <v>368.01</v>
       </c>
       <c r="F5" t="n">
-        <v>3504</v>
+        <v>2941</v>
       </c>
       <c r="G5" t="n">
-        <v>4298.95</v>
+        <v>3886.36</v>
       </c>
       <c r="H5" t="n">
-        <v>112</v>
+        <v>957</v>
       </c>
       <c r="I5" t="n">
-        <v>5543</v>
+        <v>4368</v>
       </c>
       <c r="J5" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="S5" t="n">
-        <v>6662</v>
+        <v>5430</v>
       </c>
       <c r="T5" t="n">
-        <v>113</v>
+        <v>959</v>
       </c>
       <c r="U5" t="n">
-        <v>5543</v>
+        <v>4368</v>
       </c>
       <c r="V5" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="W5" t="n">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="X5" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="AE5" t="n">
-        <v>6661</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -993,91 +981,91 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4212</v>
+        <v>3529</v>
       </c>
       <c r="D6" t="n">
+        <v>232</v>
+      </c>
+      <c r="E6" t="n">
+        <v>178.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2619</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2988.02</v>
+      </c>
+      <c r="H6" t="n">
         <v>382</v>
       </c>
-      <c r="E6" t="n">
-        <v>215.96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3027</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3137.63</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="S6" t="n">
-        <v>3521</v>
+        <v>2924</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="U6" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="AE6" t="n">
-        <v>3521</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="7">
@@ -1092,91 +1080,91 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1372</v>
+        <v>1025</v>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>124.07</v>
+        <v>91.26000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>1130</v>
+        <v>831</v>
       </c>
       <c r="G7" t="n">
-        <v>1964.76</v>
+        <v>1552.14</v>
       </c>
       <c r="H7" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="I7" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="S7" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
       <c r="T7" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="U7" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="AE7" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -1191,31 +1179,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1366</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>76.42999999999999</v>
+        <v>46.71</v>
       </c>
       <c r="F8" t="n">
-        <v>691</v>
+        <v>506</v>
       </c>
       <c r="G8" t="n">
-        <v>1139.55</v>
+        <v>1024.19</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="I8" t="n">
-        <v>912</v>
+        <v>644</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1230,28 +1218,28 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="S8" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
       <c r="T8" t="n">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="U8" t="n">
-        <v>912</v>
+        <v>644</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1266,16 +1254,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="AE8" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9">
@@ -1290,91 +1278,91 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4759</v>
+        <v>3394</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="E9" t="n">
-        <v>226.55</v>
+        <v>300.61</v>
       </c>
       <c r="F9" t="n">
-        <v>3082</v>
+        <v>2103</v>
       </c>
       <c r="G9" t="n">
-        <v>3722.82</v>
+        <v>3152.57</v>
       </c>
       <c r="H9" t="n">
-        <v>745</v>
+        <v>1630</v>
       </c>
       <c r="I9" t="n">
-        <v>3557</v>
+        <v>2443</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="S9" t="n">
-        <v>4402</v>
+        <v>3153</v>
       </c>
       <c r="T9" t="n">
-        <v>748</v>
+        <v>1630</v>
       </c>
       <c r="U9" t="n">
-        <v>3555</v>
+        <v>2443</v>
       </c>
       <c r="V9" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="W9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="AE9" t="n">
-        <v>4399</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="10">
@@ -1389,91 +1377,91 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7784</v>
+        <v>5829</v>
       </c>
       <c r="D10" t="n">
-        <v>440</v>
+        <v>197</v>
       </c>
       <c r="E10" t="n">
-        <v>345.73</v>
+        <v>261.38</v>
       </c>
       <c r="F10" t="n">
-        <v>5439</v>
+        <v>4224</v>
       </c>
       <c r="G10" t="n">
-        <v>4819.38</v>
+        <v>4243.03</v>
       </c>
       <c r="H10" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="I10" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="J10" t="n">
-        <v>780</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="M10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>6749</v>
+        <v>6348</v>
       </c>
       <c r="S10" t="n">
-        <v>5894</v>
+        <v>4331</v>
       </c>
       <c r="T10" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="U10" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="V10" t="n">
-        <v>780</v>
+        <v>295</v>
       </c>
       <c r="W10" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>6749</v>
+        <v>6347</v>
       </c>
       <c r="AE10" t="n">
-        <v>5894</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="11">
@@ -1488,91 +1476,91 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4063</v>
+        <v>2800</v>
       </c>
       <c r="D11" t="n">
-        <v>976</v>
+        <v>525</v>
       </c>
       <c r="E11" t="n">
-        <v>1163.11</v>
+        <v>1104.51</v>
       </c>
       <c r="F11" t="n">
-        <v>1778</v>
+        <v>1397</v>
       </c>
       <c r="G11" t="n">
-        <v>4284.68</v>
+        <v>4044.11</v>
       </c>
       <c r="H11" t="n">
-        <v>980</v>
+        <v>2620</v>
       </c>
       <c r="I11" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="J11" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>8991</v>
+        <v>8450</v>
       </c>
       <c r="S11" t="n">
-        <v>7916</v>
+        <v>5652</v>
       </c>
       <c r="T11" t="n">
-        <v>981</v>
+        <v>2620</v>
       </c>
       <c r="U11" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="V11" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="W11" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
         <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>8991</v>
+        <v>8448</v>
       </c>
       <c r="AE11" t="n">
-        <v>7915</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="12">
@@ -1587,91 +1575,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3536</v>
+        <v>2810</v>
       </c>
       <c r="D12" t="n">
-        <v>267</v>
+        <v>173</v>
       </c>
       <c r="E12" t="n">
-        <v>620.52</v>
+        <v>440.02</v>
       </c>
       <c r="F12" t="n">
-        <v>2568</v>
+        <v>2073</v>
       </c>
       <c r="G12" t="n">
-        <v>4522.81</v>
+        <v>4132.93</v>
       </c>
       <c r="H12" t="n">
-        <v>432</v>
+        <v>1416</v>
       </c>
       <c r="I12" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="J12" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="S12" t="n">
-        <v>5057</v>
+        <v>3797</v>
       </c>
       <c r="T12" t="n">
-        <v>434</v>
+        <v>1418</v>
       </c>
       <c r="U12" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="V12" t="n">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="W12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="AC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="AE12" t="n">
-        <v>5055</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="13">
@@ -1686,37 +1674,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3104</v>
+        <v>2092</v>
       </c>
       <c r="D13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E13" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2410.08</v>
+      </c>
+      <c r="H13" t="n">
+        <v>751</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86</v>
+      </c>
+      <c r="L13" t="n">
         <v>70</v>
       </c>
-      <c r="E13" t="n">
-        <v>95.26000000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2429</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3072.17</v>
-      </c>
-      <c r="H13" t="n">
-        <v>174</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1652</v>
-      </c>
-      <c r="J13" t="n">
-        <v>152</v>
-      </c>
-      <c r="K13" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" t="n">
-        <v>134</v>
-      </c>
       <c r="M13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -1725,34 +1713,34 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R13" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="S13" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
       <c r="T13" t="n">
-        <v>174</v>
+        <v>751</v>
       </c>
       <c r="U13" t="n">
-        <v>1652</v>
+        <v>1248</v>
       </c>
       <c r="V13" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="X13" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
@@ -1761,16 +1749,16 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AC13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="AE13" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="14">
@@ -1785,91 +1773,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10443</v>
+        <v>8544</v>
       </c>
       <c r="D14" t="n">
-        <v>738</v>
+        <v>484</v>
       </c>
       <c r="E14" t="n">
-        <v>682.41</v>
+        <v>531.38</v>
       </c>
       <c r="F14" t="n">
-        <v>7740</v>
+        <v>6358</v>
       </c>
       <c r="G14" t="n">
-        <v>6969.06</v>
+        <v>6410.83</v>
       </c>
       <c r="H14" t="n">
-        <v>149</v>
+        <v>1393</v>
       </c>
       <c r="I14" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="J14" t="n">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="S14" t="n">
-        <v>10172</v>
+        <v>8195</v>
       </c>
       <c r="T14" t="n">
-        <v>149</v>
+        <v>1394</v>
       </c>
       <c r="U14" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="V14" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="W14" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="AE14" t="n">
-        <v>10171</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="15">
@@ -1884,28 +1872,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1385</v>
+        <v>1241</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>15.3</v>
       </c>
       <c r="F15" t="n">
-        <v>1172</v>
+        <v>1049</v>
       </c>
       <c r="G15" t="n">
-        <v>1692.39</v>
+        <v>1611.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I15" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1917,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1929,19 +1917,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="S15" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="U15" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1953,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -1965,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="AE15" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">
@@ -1983,34 +1971,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>128.85</v>
+        <v>30.63</v>
       </c>
       <c r="F16" t="n">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="G16" t="n">
-        <v>479.11</v>
+        <v>475.55</v>
       </c>
       <c r="H16" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="I16" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2028,25 +2016,25 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="S16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="T16" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="U16" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2064,10 +2052,10 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="AE16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17">
@@ -2082,91 +2070,91 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3039</v>
+        <v>2184</v>
       </c>
       <c r="D17" t="n">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="E17" t="n">
-        <v>264.9</v>
+        <v>252.69</v>
       </c>
       <c r="F17" t="n">
-        <v>2375</v>
+        <v>1651</v>
       </c>
       <c r="G17" t="n">
-        <v>2542.17</v>
+        <v>1833.13</v>
       </c>
       <c r="H17" t="n">
-        <v>275</v>
+        <v>815</v>
       </c>
       <c r="I17" t="n">
-        <v>2176</v>
+        <v>1522</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2921</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2106</v>
+      </c>
+      <c r="T17" t="n">
+        <v>815</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1522</v>
+      </c>
+      <c r="V17" t="n">
+        <v>53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>3009</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2734</v>
-      </c>
-      <c r="T17" t="n">
-        <v>276</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2176</v>
-      </c>
-      <c r="V17" t="n">
-        <v>10</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>10</v>
-      </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3009</v>
+        <v>2921</v>
       </c>
       <c r="AE17" t="n">
-        <v>2733</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>
